--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -618,7 +618,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4025-25mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£10.52</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -740,7 +740,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4030-30mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£12.29</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -862,7 +862,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-tb4040-40mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£14.93</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4050-50mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£17.14</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://www.humancapitalconsultants.com/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£19.85</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4060-60mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£20.47</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>£23.15</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4070-70mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£22.34</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4075-75mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4080-80mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£24.64</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4090-90mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£27.5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-ga4100-100mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£28.71</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4110-110mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£32.97</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4120-120mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£34.0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4130-130mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£38.6</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4140-140mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£43.83</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4150-150mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£42.21</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4165-165mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£653.19</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4200-200mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£861.09</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4025-38mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4040-53mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£44.24</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4050-63mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£52.32</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4060-73mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£55.49</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4050-50mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£41.25</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4075-75mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£39.38</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff689781eb5+80197]
-	GetHandleVerifier [0x0x7ff689781f10+80288]
-	(No symbol) [0x0x7ff6895002fa]
-	(No symbol) [0x0x7ff689557cd7]
-	(No symbol) [0x0x7ff689557f9c]
-	(No symbol) [0x0x7ff6895aba87]
-	(No symbol) [0x0x7ff6895803bf]
-	(No symbol) [0x0x7ff6895a87fb]
-	(No symbol) [0x0x7ff689580153]
-	(No symbol) [0x0x7ff689548b02]
-	(No symbol) [0x0x7ff6895498d3]
-	GetHandleVerifier [0x0x7ff689a3e83d+2949837]
-	GetHandleVerifier [0x0x7ff689a38c6a+2926330]
-	GetHandleVerifier [0x0x7ff689a586c7+3055959]
-	GetHandleVerifier [0x0x7ff68979cfee+191102]
-	GetHandleVerifier [0x0x7ff6897a50af+224063]
-	GetHandleVerifier [0x0x7ff68978af64+117236]
-	GetHandleVerifier [0x0x7ff68978b119+117673]
-	GetHandleVerifier [0x0x7ff6897710a8+11064]
+	GetHandleVerifier [0x0x7ff668451eb5+80197]
+	GetHandleVerifier [0x0x7ff668451f10+80288]
+	(No symbol) [0x0x7ff6681d02fa]
+	(No symbol) [0x0x7ff668227cd7]
+	(No symbol) [0x0x7ff668227f9c]
+	(No symbol) [0x0x7ff66827ba87]
+	(No symbol) [0x0x7ff6682503bf]
+	(No symbol) [0x0x7ff6682787fb]
+	(No symbol) [0x0x7ff668250153]
+	(No symbol) [0x0x7ff668218b02]
+	(No symbol) [0x0x7ff6682198d3]
+	GetHandleVerifier [0x0x7ff66870e83d+2949837]
+	GetHandleVerifier [0x0x7ff668708c6a+2926330]
+	GetHandleVerifier [0x0x7ff6687286c7+3055959]
+	GetHandleVerifier [0x0x7ff66846cfee+191102]
+	GetHandleVerifier [0x0x7ff6684750af+224063]
+	GetHandleVerifier [0x0x7ff66845af64+117236]
+	GetHandleVerifier [0x0x7ff66845b119+117673]
+	GetHandleVerifier [0x0x7ff6684410a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4100-100mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£40.53</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-90mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£1057.71</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-115mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£1126.15</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-140mm/ (Caused by SSLError(SSLError(1, '[SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1006)')))</t>
+          <t>£1096.66</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-09-2025.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£10.65</t>
+          <t>£10.55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£19.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£23.15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.80</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£27.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£26.64</t>
+          <t>£26.20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£40.68</t>
+          <t>£38.70</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£40.62</t>
+          <t>£39.50</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£28.70</t>
+          <t>£28.41</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£34.65</t>
+          <t>£34.30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£37.62</t>
+          <t>£37.24</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£42.88</t>
+          <t>£42.45</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff668451eb5+80197]
-	GetHandleVerifier [0x0x7ff668451f10+80288]
-	(No symbol) [0x0x7ff6681d02fa]
-	(No symbol) [0x0x7ff668227cd7]
-	(No symbol) [0x0x7ff668227f9c]
-	(No symbol) [0x0x7ff66827ba87]
-	(No symbol) [0x0x7ff6682503bf]
-	(No symbol) [0x0x7ff6682787fb]
-	(No symbol) [0x0x7ff668250153]
-	(No symbol) [0x0x7ff668218b02]
-	(No symbol) [0x0x7ff6682198d3]
-	GetHandleVerifier [0x0x7ff66870e83d+2949837]
-	GetHandleVerifier [0x0x7ff668708c6a+2926330]
-	GetHandleVerifier [0x0x7ff6687286c7+3055959]
-	GetHandleVerifier [0x0x7ff66846cfee+191102]
-	GetHandleVerifier [0x0x7ff6684750af+224063]
-	GetHandleVerifier [0x0x7ff66845af64+117236]
-	GetHandleVerifier [0x0x7ff66845b119+117673]
-	GetHandleVerifier [0x0x7ff6684410a8+11064]
+	GetHandleVerifier [0x0x7ff685281eb5+80197]
+	GetHandleVerifier [0x0x7ff685281f10+80288]
+	(No symbol) [0x0x7ff6850002fa]
+	(No symbol) [0x0x7ff685057cd7]
+	(No symbol) [0x0x7ff685057f9c]
+	(No symbol) [0x0x7ff6850aba87]
+	(No symbol) [0x0x7ff6850803bf]
+	(No symbol) [0x0x7ff6850a87fb]
+	(No symbol) [0x0x7ff685080153]
+	(No symbol) [0x0x7ff685048b02]
+	(No symbol) [0x0x7ff6850498d3]
+	GetHandleVerifier [0x0x7ff68553e83d+2949837]
+	GetHandleVerifier [0x0x7ff685538c6a+2926330]
+	GetHandleVerifier [0x0x7ff6855586c7+3055959]
+	GetHandleVerifier [0x0x7ff68529cfee+191102]
+	GetHandleVerifier [0x0x7ff6852a50af+224063]
+	GetHandleVerifier [0x0x7ff68528af64+117236]
+	GetHandleVerifier [0x0x7ff68528b119+117673]
+	GetHandleVerifier [0x0x7ff6852710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
